--- a/AI_DigitalFactory_개발정의.xlsx
+++ b/AI_DigitalFactory_개발정의.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1060,88 +1060,44 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>wafer_agent/</t>
+          <t>Cell 10</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>main.py</t>
+          <t>Qwen 단건 테스트</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>CLI 진입점</t>
+          <t>분류·대응 LLM 단건 확인</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>python -m wafer_agent.main</t>
+          <t>run_classification, run_action_decision</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>wafer_agent/</t>
+          <t>Cell 11</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>simulator.py</t>
+          <t>시각화</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>센서 데이터 생성</t>
+          <t>matplotlib 차트 + GT 오버레이</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>generate_sensor_data()</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>wafer_agent/</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>llm.py</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>LLM 통합 (mock/qwen/anthropic)</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>load_qwen_model, invoke_structured</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>wafer_agent/</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>agent/graph.py</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>LangGraph StateGraph</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>build_agent(), run_anomaly_pipeline()</t>
+          <t>events, sensor_df</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1230,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>패키지</t>
+          <t>구조 단순화</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>wafer_agent/ 모듈 구조 추가</t>
+          <t>Colab 전용 — wafer_agent/ .py 패키지 제거, 노트북 단일화</t>
         </is>
       </c>
     </row>
